--- a/2026/ЗАВОДЫ/Останкино/ОПТы/01,26/06,01,26 Ост КИ Табота сап 11,01,26/Заказ Новое Время 11,01. Табота№8.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/ОПТы/01,26/06,01,26 Ост КИ Табота сап 11,01,26/Заказ Новое Время 11,01. Табота№8.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV_Poliakov_PRS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\2026\ЗАВОДЫ\Останкино\ОПТы\01,26\06,01,26 Ост КИ Табота сап 11,01,26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F55BEDB-9293-4026-96D5-08D0C0A01E13}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A82580-318B-4F59-827B-B282A030AA60}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11700" yWindow="930" windowWidth="17100" windowHeight="14670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Бланк" sheetId="1" r:id="rId1"/>
@@ -1578,7 +1578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K1668"/>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="K9" s="28"/>
     </row>
-    <row r="10" spans="1:11" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="61"/>
       <c r="B10" s="46" t="s">
         <v>19</v>
@@ -1720,7 +1720,7 @@
       <c r="I10" s="46"/>
       <c r="J10" s="47"/>
     </row>
-    <row r="11" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A11" s="59" t="str">
         <f t="shared" ref="A11:A32" si="0">RIGHT(D11,4)</f>
         <v>6415</v>
@@ -1751,7 +1751,7 @@
       <c r="J11" s="29"/>
       <c r="K11" s="27"/>
     </row>
-    <row r="12" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A12" s="59" t="str">
         <f t="shared" si="0"/>
         <v>4063</v>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="J12" s="29"/>
     </row>
-    <row r="13" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="59" t="str">
         <f t="shared" si="0"/>
         <v>6333</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="J13" s="29"/>
     </row>
-    <row r="14" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="59" t="str">
         <f t="shared" si="0"/>
         <v>4558</v>
@@ -1837,7 +1837,7 @@
       <c r="I14" s="14"/>
       <c r="J14" s="29"/>
     </row>
-    <row r="15" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="59" t="str">
         <f t="shared" si="0"/>
         <v>6978</v>
@@ -1861,7 +1861,7 @@
       <c r="I15" s="14"/>
       <c r="J15" s="29"/>
     </row>
-    <row r="16" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="59" t="str">
         <f t="shared" si="0"/>
         <v>4561</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="J17" s="29"/>
     </row>
-    <row r="18" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="59" t="str">
         <f t="shared" si="0"/>
         <v>6769</v>
@@ -1941,7 +1941,7 @@
       <c r="I18" s="14"/>
       <c r="J18" s="29"/>
     </row>
-    <row r="19" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="59" t="str">
         <f t="shared" si="0"/>
         <v>6861</v>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="J19" s="29"/>
     </row>
-    <row r="20" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="59" t="str">
         <f t="shared" si="0"/>
         <v>6340</v>
@@ -1997,7 +1997,7 @@
       <c r="I20" s="14"/>
       <c r="J20" s="29"/>
     </row>
-    <row r="21" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="59" t="str">
         <f t="shared" si="0"/>
         <v>6341</v>
@@ -2023,7 +2023,7 @@
       <c r="I21" s="76"/>
       <c r="J21" s="76"/>
     </row>
-    <row r="22" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="59" t="str">
         <f t="shared" si="0"/>
         <v>6862</v>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="J23" s="29"/>
     </row>
-    <row r="24" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="59" t="str">
         <f t="shared" si="0"/>
         <v>6392</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="J24" s="29"/>
     </row>
-    <row r="25" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="59" t="str">
         <f t="shared" si="0"/>
         <v>5851</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="J25" s="29"/>
     </row>
-    <row r="26" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="59" t="str">
         <f t="shared" si="0"/>
         <v>6353</v>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="J26" s="29"/>
     </row>
-    <row r="27" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="59" t="str">
         <f t="shared" si="0"/>
         <v>6268</v>
@@ -2201,7 +2201,7 @@
       <c r="I27" s="14"/>
       <c r="J27" s="29"/>
     </row>
-    <row r="28" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="59" t="str">
         <f t="shared" si="0"/>
         <v>6324</v>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="J28" s="29"/>
     </row>
-    <row r="29" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="59" t="str">
         <f t="shared" si="0"/>
         <v>6498</v>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="J29" s="29"/>
     </row>
-    <row r="30" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="59" t="str">
         <f t="shared" si="0"/>
         <v>7125</v>
@@ -2287,7 +2287,7 @@
       <c r="I30" s="14"/>
       <c r="J30" s="29"/>
     </row>
-    <row r="31" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="59" t="str">
         <f t="shared" si="0"/>
         <v>2675</v>
@@ -2311,7 +2311,7 @@
       <c r="I31" s="14"/>
       <c r="J31" s="29"/>
     </row>
-    <row r="32" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="59" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2328,7 +2328,7 @@
       <c r="I32" s="46"/>
       <c r="J32" s="47"/>
     </row>
-    <row r="33" spans="1:11" s="68" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" s="68" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A33" s="59">
         <v>7255</v>
       </c>
@@ -2358,7 +2358,7 @@
       <c r="J33" s="67"/>
       <c r="K33" s="27"/>
     </row>
-    <row r="34" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="59" t="str">
         <f t="shared" ref="A34:A46" si="2">RIGHT(D34,4)</f>
         <v>6602</v>
@@ -2418,7 +2418,7 @@
       <c r="J35" s="29"/>
       <c r="K35" s="27"/>
     </row>
-    <row r="36" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="59" t="str">
         <f t="shared" si="2"/>
         <v>5819</v>
@@ -2449,7 +2449,7 @@
       <c r="J36" s="29"/>
       <c r="K36" s="27"/>
     </row>
-    <row r="37" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="59" t="str">
         <f t="shared" si="2"/>
         <v>6762</v>
@@ -2476,7 +2476,7 @@
       <c r="J37" s="29"/>
       <c r="K37" s="27"/>
     </row>
-    <row r="38" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="59" t="str">
         <f t="shared" si="2"/>
         <v>6765</v>
@@ -2503,7 +2503,7 @@
       <c r="J38" s="29"/>
       <c r="K38" s="27"/>
     </row>
-    <row r="39" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="59" t="str">
         <f t="shared" si="2"/>
         <v>6759</v>
@@ -2530,7 +2530,7 @@
       <c r="J39" s="29"/>
       <c r="K39" s="27"/>
     </row>
-    <row r="40" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="59" t="str">
         <f t="shared" si="2"/>
         <v>7082</v>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="J40" s="29"/>
     </row>
-    <row r="41" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="59" t="str">
         <f t="shared" si="2"/>
         <v>6767</v>
@@ -2643,7 +2643,7 @@
       <c r="J43" s="29"/>
       <c r="K43" s="27"/>
     </row>
-    <row r="44" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="59" t="str">
         <f t="shared" si="2"/>
         <v>6475</v>
@@ -2674,7 +2674,7 @@
       <c r="J44" s="29"/>
       <c r="K44" s="27"/>
     </row>
-    <row r="45" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="59" t="str">
         <f t="shared" si="2"/>
         <v>6713</v>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="J45" s="29"/>
     </row>
-    <row r="46" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="59" t="str">
         <f t="shared" si="2"/>
         <v>6069</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="J46" s="29"/>
     </row>
-    <row r="47" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="59">
         <v>7284</v>
       </c>
@@ -2759,7 +2759,7 @@
       <c r="I47" s="14"/>
       <c r="J47" s="29"/>
     </row>
-    <row r="48" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="59" t="str">
         <f t="shared" ref="A48:A79" si="3">RIGHT(D48,4)</f>
         <v>6764</v>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="J48" s="29"/>
     </row>
-    <row r="49" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="59" t="str">
         <f t="shared" si="3"/>
         <v>6829</v>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="J49" s="29"/>
     </row>
-    <row r="50" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="59" t="str">
         <f t="shared" si="3"/>
         <v>7075</v>
@@ -2843,7 +2843,7 @@
       <c r="I50" s="14"/>
       <c r="J50" s="29"/>
     </row>
-    <row r="51" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="59" t="str">
         <f t="shared" si="3"/>
         <v>7073</v>
@@ -2869,7 +2869,7 @@
       <c r="I51" s="14"/>
       <c r="J51" s="29"/>
     </row>
-    <row r="52" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="59" t="str">
         <f t="shared" si="3"/>
         <v>6616</v>
@@ -2895,7 +2895,7 @@
       <c r="I52" s="14"/>
       <c r="J52" s="29"/>
     </row>
-    <row r="53" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="59" t="str">
         <f t="shared" si="3"/>
         <v>7074</v>
@@ -2921,7 +2921,7 @@
       <c r="I53" s="14"/>
       <c r="J53" s="29"/>
     </row>
-    <row r="54" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="59" t="str">
         <f t="shared" si="3"/>
         <v>6761</v>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="J54" s="29"/>
     </row>
-    <row r="55" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="59" t="str">
         <f t="shared" si="3"/>
         <v>7080</v>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="J55" s="29"/>
     </row>
-    <row r="56" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A56" s="59" t="str">
         <f t="shared" si="3"/>
         <v>7066</v>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="J56" s="29"/>
     </row>
-    <row r="57" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="59" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3028,7 +3028,7 @@
       <c r="I57" s="46"/>
       <c r="J57" s="47"/>
     </row>
-    <row r="58" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A58" s="59" t="str">
         <f t="shared" si="3"/>
         <v>7001</v>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="J58" s="76"/>
     </row>
-    <row r="59" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="59" t="str">
         <f t="shared" si="3"/>
         <v>6527</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="J59" s="29"/>
     </row>
-    <row r="60" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="59" t="str">
         <f t="shared" si="3"/>
         <v>6550</v>
@@ -3114,7 +3114,7 @@
       <c r="I60" s="14"/>
       <c r="J60" s="29"/>
     </row>
-    <row r="61" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="59" t="str">
         <f t="shared" si="3"/>
         <v>6608</v>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="J61" s="29"/>
     </row>
-    <row r="62" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="59" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -3161,7 +3161,7 @@
       <c r="I62" s="46"/>
       <c r="J62" s="47"/>
     </row>
-    <row r="63" spans="1:10" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A63" s="59" t="str">
         <f t="shared" si="3"/>
         <v>6586</v>
@@ -3187,7 +3187,7 @@
       <c r="I63" s="14"/>
       <c r="J63" s="29"/>
     </row>
-    <row r="64" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="59" t="str">
         <f t="shared" si="3"/>
         <v>7144</v>
@@ -3213,7 +3213,7 @@
       <c r="I64" s="14"/>
       <c r="J64" s="29"/>
     </row>
-    <row r="65" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="59" t="str">
         <f t="shared" si="3"/>
         <v>7146</v>
@@ -3263,7 +3263,7 @@
       <c r="I66" s="14"/>
       <c r="J66" s="29"/>
     </row>
-    <row r="67" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="59" t="str">
         <f t="shared" si="3"/>
         <v>7131</v>
@@ -3287,7 +3287,7 @@
       <c r="I67" s="14"/>
       <c r="J67" s="29"/>
     </row>
-    <row r="68" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="59" t="str">
         <f t="shared" si="3"/>
         <v>7233</v>
@@ -3313,7 +3313,7 @@
       <c r="I68" s="14"/>
       <c r="J68" s="29"/>
     </row>
-    <row r="69" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="59" t="str">
         <f t="shared" si="3"/>
         <v>6666</v>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="J69" s="29"/>
     </row>
-    <row r="70" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="59" t="str">
         <f t="shared" si="3"/>
         <v>7173</v>
@@ -3397,7 +3397,7 @@
       <c r="I71" s="14"/>
       <c r="J71" s="29"/>
     </row>
-    <row r="72" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="59" t="str">
         <f t="shared" si="3"/>
         <v>6773</v>
@@ -3455,7 +3455,7 @@
       <c r="I73" s="14"/>
       <c r="J73" s="29"/>
     </row>
-    <row r="74" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="59" t="str">
         <f t="shared" si="3"/>
         <v>6683</v>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="J74" s="29"/>
     </row>
-    <row r="75" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="59" t="str">
         <f t="shared" si="3"/>
         <v>5489</v>
@@ -3509,7 +3509,7 @@
       <c r="I75" s="14"/>
       <c r="J75" s="29"/>
     </row>
-    <row r="76" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="59" t="str">
         <f t="shared" si="3"/>
         <v>6787</v>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="J77" s="29"/>
     </row>
-    <row r="78" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="59" t="str">
         <f t="shared" si="3"/>
         <v>6701</v>
@@ -3629,7 +3629,7 @@
       <c r="I79" s="14"/>
       <c r="J79" s="29"/>
     </row>
-    <row r="80" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="59" t="str">
         <f t="shared" ref="A80:A111" si="6">RIGHT(D80,4)</f>
         <v>6684</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="J80" s="29"/>
     </row>
-    <row r="81" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="59" t="str">
         <f t="shared" si="6"/>
         <v>6689</v>
@@ -3797,7 +3797,7 @@
       <c r="I85" s="14"/>
       <c r="J85" s="29"/>
     </row>
-    <row r="86" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="59" t="str">
         <f t="shared" si="6"/>
         <v>5341</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="J87" s="29"/>
     </row>
-    <row r="88" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="59" t="str">
         <f t="shared" si="6"/>
         <v>6790</v>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="J88" s="71"/>
     </row>
-    <row r="89" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="59" t="str">
         <f t="shared" si="6"/>
         <v>7133</v>
@@ -3911,7 +3911,7 @@
       <c r="I89" s="14"/>
       <c r="J89" s="71"/>
     </row>
-    <row r="90" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="59" t="str">
         <f t="shared" si="6"/>
         <v>6791</v>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="J90" s="71"/>
     </row>
-    <row r="91" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="59" t="str">
         <f t="shared" si="6"/>
         <v>6792</v>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="J91" s="71"/>
     </row>
-    <row r="92" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="59" t="str">
         <f t="shared" si="6"/>
         <v>6564</v>
@@ -3993,7 +3993,7 @@
       <c r="I92" s="14"/>
       <c r="J92" s="71"/>
     </row>
-    <row r="93" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="59" t="str">
         <f t="shared" si="6"/>
         <v>7238</v>
@@ -4019,7 +4019,7 @@
       <c r="I93" s="14"/>
       <c r="J93" s="71"/>
     </row>
-    <row r="94" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="59" t="str">
         <f t="shared" si="6"/>
         <v>6565</v>
@@ -4045,7 +4045,7 @@
       <c r="I94" s="14"/>
       <c r="J94" s="71"/>
     </row>
-    <row r="95" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="59" t="str">
         <f t="shared" si="6"/>
         <v>7240</v>
@@ -4071,7 +4071,7 @@
       <c r="I95" s="14"/>
       <c r="J95" s="71"/>
     </row>
-    <row r="96" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="59" t="str">
         <f t="shared" si="6"/>
         <v>7236</v>
@@ -4125,7 +4125,7 @@
       <c r="I97" s="14"/>
       <c r="J97" s="71"/>
     </row>
-    <row r="98" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="59" t="str">
         <f t="shared" si="6"/>
         <v>6459</v>
@@ -4151,7 +4151,7 @@
       <c r="I98" s="14"/>
       <c r="J98" s="71"/>
     </row>
-    <row r="99" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="59" t="str">
         <f t="shared" si="6"/>
         <v>7107</v>
@@ -4177,7 +4177,7 @@
       <c r="I99" s="14"/>
       <c r="J99" s="71"/>
     </row>
-    <row r="100" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="59" t="str">
         <f t="shared" si="6"/>
         <v>6793</v>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="J100" s="71"/>
     </row>
-    <row r="101" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="59" t="str">
         <f t="shared" si="6"/>
         <v>6794</v>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="J101" s="71"/>
     </row>
-    <row r="102" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="59" t="str">
         <f t="shared" si="6"/>
         <v>6665</v>
@@ -4259,7 +4259,7 @@
       <c r="I102" s="14"/>
       <c r="J102" s="71"/>
     </row>
-    <row r="103" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="59" t="str">
         <f t="shared" si="6"/>
         <v>6795</v>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="J103" s="71"/>
     </row>
-    <row r="104" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="59" t="str">
         <f t="shared" si="6"/>
         <v>6796</v>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="J104" s="71"/>
     </row>
-    <row r="105" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="59" t="str">
         <f t="shared" si="6"/>
         <v>6804</v>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="J105" s="71"/>
     </row>
-    <row r="106" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="59" t="str">
         <f t="shared" si="6"/>
         <v>6803</v>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="J106" s="71"/>
     </row>
-    <row r="107" spans="1:11" s="68" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" s="68" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A107" s="59" t="str">
         <f t="shared" si="6"/>
         <v>6807</v>
@@ -4400,7 +4400,7 @@
       <c r="J107" s="71"/>
       <c r="K107" s="27"/>
     </row>
-    <row r="108" spans="1:11" s="68" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" s="68" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="59" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -4418,7 +4418,7 @@
       <c r="J108" s="47"/>
       <c r="K108" s="27"/>
     </row>
-    <row r="109" spans="1:11" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A109" s="59" t="str">
         <f t="shared" si="6"/>
         <v>5931</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="J109" s="67"/>
     </row>
-    <row r="110" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="59" t="str">
         <f t="shared" si="6"/>
         <v>6834</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="J110" s="76"/>
     </row>
-    <row r="111" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="59" t="str">
         <f t="shared" si="6"/>
         <v>6454</v>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="J111" s="29"/>
     </row>
-    <row r="112" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="59" t="str">
         <f t="shared" ref="A112:A143" si="8">RIGHT(D112,4)</f>
         <v>5708</v>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="J112" s="29"/>
     </row>
-    <row r="113" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="59" t="str">
         <f t="shared" si="8"/>
         <v>0614</v>
@@ -4562,7 +4562,7 @@
       <c r="I113" s="14"/>
       <c r="J113" s="29"/>
     </row>
-    <row r="114" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="59" t="str">
         <f t="shared" si="8"/>
         <v>1146</v>
@@ -4586,7 +4586,7 @@
       <c r="I114" s="14"/>
       <c r="J114" s="29"/>
     </row>
-    <row r="115" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="59" t="str">
         <f t="shared" si="8"/>
         <v>4154</v>
@@ -4610,7 +4610,7 @@
       <c r="I115" s="14"/>
       <c r="J115" s="29"/>
     </row>
-    <row r="116" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="59" t="str">
         <f t="shared" si="8"/>
         <v>6967</v>
@@ -4636,7 +4636,7 @@
       <c r="I116" s="14"/>
       <c r="J116" s="29"/>
     </row>
-    <row r="117" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="59" t="str">
         <f t="shared" si="8"/>
         <v>4993</v>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="J117" s="29"/>
     </row>
-    <row r="118" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="59" t="str">
         <f t="shared" si="8"/>
         <v>6937</v>
@@ -4692,7 +4692,7 @@
       <c r="I118" s="14"/>
       <c r="J118" s="29"/>
     </row>
-    <row r="119" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="59" t="str">
         <f t="shared" si="8"/>
         <v>5682</v>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="J119" s="29"/>
     </row>
-    <row r="120" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="59" t="str">
         <f t="shared" si="8"/>
         <v>5679</v>
@@ -4748,7 +4748,7 @@
       <c r="I120" s="14"/>
       <c r="J120" s="29"/>
     </row>
-    <row r="121" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="59" t="str">
         <f t="shared" si="8"/>
         <v>4117</v>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="J121" s="29"/>
     </row>
-    <row r="122" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="59" t="str">
         <f t="shared" si="8"/>
         <v>5483</v>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="J122" s="29"/>
     </row>
-    <row r="123" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="59" t="str">
         <f t="shared" si="8"/>
         <v>6453</v>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="J123" s="29"/>
     </row>
-    <row r="124" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="59" t="str">
         <f t="shared" si="8"/>
         <v>6557</v>
@@ -4864,7 +4864,7 @@
       <c r="I124" s="14"/>
       <c r="J124" s="29"/>
     </row>
-    <row r="125" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="59" t="str">
         <f t="shared" si="8"/>
         <v>6228</v>
@@ -4890,7 +4890,7 @@
       <c r="I125" s="14"/>
       <c r="J125" s="29"/>
     </row>
-    <row r="126" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="59" t="str">
         <f t="shared" si="8"/>
         <v>6221</v>
@@ -4916,7 +4916,7 @@
       <c r="I126" s="14"/>
       <c r="J126" s="29"/>
     </row>
-    <row r="127" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A127" s="59" t="str">
         <f t="shared" si="8"/>
         <v>3287</v>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="J127" s="29"/>
     </row>
-    <row r="128" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4963,7 +4963,7 @@
       <c r="I128" s="46"/>
       <c r="J128" s="47"/>
     </row>
-    <row r="129" spans="1:11" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A129" s="59" t="str">
         <f t="shared" si="8"/>
         <v>6866</v>
@@ -4987,7 +4987,7 @@
       <c r="I129" s="14"/>
       <c r="J129" s="29"/>
     </row>
-    <row r="130" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="59" t="str">
         <f t="shared" si="8"/>
         <v>3215</v>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="J130" s="29"/>
     </row>
-    <row r="131" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="59" t="str">
         <f t="shared" si="8"/>
         <v>6025</v>
@@ -5041,7 +5041,7 @@
       <c r="I131" s="14"/>
       <c r="J131" s="29"/>
     </row>
-    <row r="132" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="59" t="str">
         <f t="shared" si="8"/>
         <v>6470</v>
@@ -5067,7 +5067,7 @@
       <c r="I132" s="14"/>
       <c r="J132" s="29"/>
     </row>
-    <row r="133" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="59" t="str">
         <f t="shared" si="8"/>
         <v>4584</v>
@@ -5091,7 +5091,7 @@
       <c r="I133" s="14"/>
       <c r="J133" s="29"/>
     </row>
-    <row r="134" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="59" t="str">
         <f t="shared" si="8"/>
         <v>6472</v>
@@ -5115,7 +5115,7 @@
       <c r="I134" s="14"/>
       <c r="J134" s="29"/>
     </row>
-    <row r="135" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="59" t="str">
         <f t="shared" si="8"/>
         <v>5452</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="J135" s="29"/>
     </row>
-    <row r="136" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="59" t="str">
         <f t="shared" si="8"/>
         <v>5495</v>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="J136" s="29"/>
     </row>
-    <row r="137" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="59" t="str">
         <f t="shared" si="8"/>
         <v>6495</v>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="J137" s="29"/>
     </row>
-    <row r="138" spans="1:11" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="59" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5222,7 +5222,7 @@
       <c r="I138" s="46"/>
       <c r="J138" s="47"/>
     </row>
-    <row r="139" spans="1:11" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A139" s="59" t="str">
         <f t="shared" si="8"/>
         <v>6448</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="J139" s="29"/>
     </row>
-    <row r="140" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="59" t="str">
         <f t="shared" si="8"/>
         <v>7090</v>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="J140" s="29"/>
     </row>
-    <row r="141" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="59" t="str">
         <f t="shared" si="8"/>
         <v>6208</v>
@@ -5308,7 +5308,7 @@
       <c r="I141" s="14"/>
       <c r="J141" s="29"/>
     </row>
-    <row r="142" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="59" t="str">
         <f t="shared" si="8"/>
         <v>7053</v>
@@ -5332,7 +5332,7 @@
       <c r="I142" s="14"/>
       <c r="J142" s="29"/>
     </row>
-    <row r="143" spans="1:11" s="70" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" s="70" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="59" t="str">
         <f t="shared" si="8"/>
         <v>7103</v>
@@ -20624,7 +20624,13 @@
       <c r="J1668" s="21"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:K144" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:K144" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
